--- a/vystupy/Sozialgebaeude_soupis.xlsx
+++ b/vystupy/Sozialgebaeude_soupis.xlsx
@@ -484,7 +484,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Párováno k nejbližšímu popisku 'P ≈ … W' (typicky 750 mm pod názvem; vzdálenost uvedena pro kontrolu). U '3x …' NENÍ ověřeno, zda výkon platí na kus, nebo celkem.</t>
+          <t>Párováno k nejbližšímu popisku 'P ≈ … W'. POTVRZENO (uživatel, 2026-10-06): výkon v popisku platí na 1 kus; u '3x …' je celkový výkon = počet × výkon. Viz sloupec 'Výkon celkem W'.</t>
         </is>
       </c>
     </row>
@@ -676,7 +676,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G51"/>
+  <dimension ref="A1:H51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -701,7 +701,7 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Výkon W (nejbližší popisek P≈)</t>
+          <t>Výkon W na 1 kus (potvrzeno uživatelem)</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
@@ -722,6 +722,11 @@
       <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Hladina</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Výkon celkem W (počet × výkon/ks)</t>
         </is>
       </c>
     </row>
@@ -751,6 +756,9 @@
           <t>Heiz Wasser +60 -Heizkörper Vorlauf</t>
         </is>
       </c>
+      <c r="H2" t="n">
+        <v>1200</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -778,6 +786,9 @@
           <t>Heiz Wasser +60 -Heizkörper Vorlauf</t>
         </is>
       </c>
+      <c r="H3" t="n">
+        <v>1200</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -805,6 +816,9 @@
           <t>Heiz Wasser +60 -Heizkörper Vorlauf</t>
         </is>
       </c>
+      <c r="H4" t="n">
+        <v>800</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -832,6 +846,9 @@
           <t>Heiz Wasser +60 -Heizkörper Vorlauf</t>
         </is>
       </c>
+      <c r="H5" t="n">
+        <v>800</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -859,6 +876,9 @@
           <t>Heiz Wasser +60 -Heizkörper Vorlauf</t>
         </is>
       </c>
+      <c r="H6" t="n">
+        <v>350</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -886,6 +906,9 @@
           <t>Heiz Wasser +60 -Heizkörper Vorlauf</t>
         </is>
       </c>
+      <c r="H7" t="n">
+        <v>1000</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -913,6 +936,9 @@
           <t>Heiz Wasser +60 -Heizkörper Vorlauf</t>
         </is>
       </c>
+      <c r="H8" t="n">
+        <v>600</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -940,6 +966,9 @@
           <t>Heiz Wasser +60 -Heizkörper Vorlauf</t>
         </is>
       </c>
+      <c r="H9" t="n">
+        <v>800</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -967,6 +996,9 @@
           <t>Heiz Wasser +60 -Heizkörper Vorlauf</t>
         </is>
       </c>
+      <c r="H10" t="n">
+        <v>800</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -994,6 +1026,9 @@
           <t>Heiz Wasser +60 -Heizkörper Vorlauf</t>
         </is>
       </c>
+      <c r="H11" t="n">
+        <v>400</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1021,6 +1056,9 @@
           <t>Heiz Wasser +60 -Heizkörper Vorlauf</t>
         </is>
       </c>
+      <c r="H12" t="n">
+        <v>3200</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1048,6 +1086,9 @@
           <t>Heiz Wasser +60 -Heizkörper Vorlauf</t>
         </is>
       </c>
+      <c r="H13" t="n">
+        <v>500</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1075,6 +1116,9 @@
           <t>Heiz Wasser +60 -Heizkörper Vorlauf</t>
         </is>
       </c>
+      <c r="H14" t="n">
+        <v>2400</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1102,6 +1146,9 @@
           <t>Heiz Wasser +60 -Heizkörper Vorlauf</t>
         </is>
       </c>
+      <c r="H15" t="n">
+        <v>700</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1129,6 +1176,9 @@
           <t>Heiz Wasser +60 -Heizkörper Vorlauf</t>
         </is>
       </c>
+      <c r="H16" t="n">
+        <v>1000</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1156,6 +1206,9 @@
           <t>Heiz Wasser +60 -Heizkörper Vorlauf</t>
         </is>
       </c>
+      <c r="H17" t="n">
+        <v>1800</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1183,6 +1236,9 @@
           <t>Heiz Wasser +60 -Heizkörper Vorlauf</t>
         </is>
       </c>
+      <c r="H18" t="n">
+        <v>4000</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1210,6 +1266,9 @@
           <t>Heiz Wasser +60 -Heizkörper Vorlauf</t>
         </is>
       </c>
+      <c r="H19" t="n">
+        <v>350</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1237,6 +1296,9 @@
           <t>Heiz Wasser +60 -Heizkörper Vorlauf</t>
         </is>
       </c>
+      <c r="H20" t="n">
+        <v>1300</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1264,6 +1326,9 @@
           <t>Heiz Wasser +60 -Heizkörper Vorlauf</t>
         </is>
       </c>
+      <c r="H21" t="n">
+        <v>500</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1291,6 +1356,9 @@
           <t>Heiz Wasser +60 -Heizkörper Vorlauf</t>
         </is>
       </c>
+      <c r="H22" t="n">
+        <v>500</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1318,6 +1386,9 @@
           <t>Heiz Wasser +60 -Heizkörper Vorlauf</t>
         </is>
       </c>
+      <c r="H23" t="n">
+        <v>350</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1345,6 +1416,9 @@
           <t>Heiz Wasser +60 -Heizkörper Vorlauf</t>
         </is>
       </c>
+      <c r="H24" t="n">
+        <v>650</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1372,6 +1446,9 @@
           <t>Heiz Wasser +60 -Heizkörper Vorlauf</t>
         </is>
       </c>
+      <c r="H25" t="n">
+        <v>500</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1399,6 +1476,9 @@
           <t>Heiz Wasser +60 -Heizkörper Vorlauf</t>
         </is>
       </c>
+      <c r="H26" t="n">
+        <v>200</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1426,6 +1506,9 @@
           <t>Heiz Wasser +60 -Heizkörper Vorlauf</t>
         </is>
       </c>
+      <c r="H27" t="n">
+        <v>650</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1453,6 +1536,9 @@
           <t>Heiz Wasser +60 -Heizkörper Vorlauf</t>
         </is>
       </c>
+      <c r="H28" t="n">
+        <v>900</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1480,6 +1566,9 @@
           <t>Heiz Wasser +60 -Heizkörper Vorlauf</t>
         </is>
       </c>
+      <c r="H29" t="n">
+        <v>4500</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1507,6 +1596,9 @@
           <t>Heiz Wasser +60 -Heizkörper Vorlauf</t>
         </is>
       </c>
+      <c r="H30" t="n">
+        <v>400</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1534,6 +1626,9 @@
           <t>Heiz Wasser +60 -Heizkörper Vorlauf</t>
         </is>
       </c>
+      <c r="H31" t="n">
+        <v>600</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1561,6 +1656,9 @@
           <t>Heiz Wasser +60 -Heizkörper Vorlauf</t>
         </is>
       </c>
+      <c r="H32" t="n">
+        <v>500</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1588,6 +1686,9 @@
           <t>Heiz Wasser +60 -Heizkörper Vorlauf</t>
         </is>
       </c>
+      <c r="H33" t="n">
+        <v>350</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1615,6 +1716,9 @@
           <t>Heiz Wasser +60 -Heizkörper Vorlauf</t>
         </is>
       </c>
+      <c r="H34" t="n">
+        <v>650</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1642,6 +1746,9 @@
           <t>Heiz Wasser +60 -Heizkörper Vorlauf</t>
         </is>
       </c>
+      <c r="H35" t="n">
+        <v>500</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1669,6 +1776,9 @@
           <t>Heiz Wasser +60 -Heizkörper Vorlauf</t>
         </is>
       </c>
+      <c r="H36" t="n">
+        <v>400</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1696,6 +1806,9 @@
           <t>Heiz Wasser +60 -Heizkörper Vorlauf</t>
         </is>
       </c>
+      <c r="H37" t="n">
+        <v>400</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1723,6 +1836,9 @@
           <t>Heiz Wasser +60 -Heizkörper Vorlauf</t>
         </is>
       </c>
+      <c r="H38" t="n">
+        <v>500</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1750,6 +1866,9 @@
           <t>Heiz Wasser +60 -Heizkörper Vorlauf</t>
         </is>
       </c>
+      <c r="H39" t="n">
+        <v>300</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1777,6 +1896,9 @@
           <t>Heiz Wasser +60 -Heizkörper Vorlauf</t>
         </is>
       </c>
+      <c r="H40" t="n">
+        <v>1200</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1804,6 +1926,9 @@
           <t>Heiz Wasser +60 -Heizkörper Vorlauf</t>
         </is>
       </c>
+      <c r="H41" t="n">
+        <v>1200</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1831,6 +1956,9 @@
           <t>Heiz Wasser +60 -Heizkörper Vorlauf</t>
         </is>
       </c>
+      <c r="H42" t="n">
+        <v>600</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1858,6 +1986,9 @@
           <t>Heiz Wasser +60 -Heizkörper Vorlauf</t>
         </is>
       </c>
+      <c r="H43" t="n">
+        <v>300</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1885,6 +2016,9 @@
           <t>Heiz Wasser +60 -Heizkörper Vorlauf</t>
         </is>
       </c>
+      <c r="H44" t="n">
+        <v>1000</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1912,6 +2046,9 @@
           <t>Heiz Wasser +60 -Heizkörper Vorlauf</t>
         </is>
       </c>
+      <c r="H45" t="n">
+        <v>1350</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1939,6 +2076,9 @@
           <t>Heiz Wasser +60 -Heizkörper Vorlauf</t>
         </is>
       </c>
+      <c r="H46" t="n">
+        <v>1100</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1966,6 +2106,9 @@
           <t>Heiz Wasser +60 -Heizkörper Vorlauf</t>
         </is>
       </c>
+      <c r="H47" t="n">
+        <v>300</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1993,6 +2136,9 @@
           <t>Heiz Wasser +60 -Heizkörper Vorlauf</t>
         </is>
       </c>
+      <c r="H48" t="n">
+        <v>1900</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2020,6 +2166,9 @@
           <t>Heiz Wasser +60 -Heizkörper Vorlauf</t>
         </is>
       </c>
+      <c r="H49" t="n">
+        <v>1100</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2047,6 +2196,9 @@
           <t>Heiz Wasser +60 -Heizkörper Vorlauf</t>
         </is>
       </c>
+      <c r="H50" t="n">
+        <v>1000</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2073,6 +2225,9 @@
         <is>
           <t>Heiz Wasser +60 -Heizkörper Vorlauf</t>
         </is>
+      </c>
+      <c r="H51" t="n">
+        <v>4800</v>
       </c>
     </row>
   </sheetData>
